--- a/apps/web/tests/fixtures/nmwc/orders-150.xlsx
+++ b/apps/web/tests/fixtures/nmwc/orders-150.xlsx
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Al Safa Grocery</v>
+        <v>Al Masa Grocery</v>
       </c>
       <c r="G53" t="str">
         <v>TAN-500-24</v>
@@ -2284,7 +2284,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Al Safa Grocery</v>
+        <v>Al Masa Grocery</v>
       </c>
       <c r="G54" t="str">
         <v>TAN-1500-6</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Al Safa Grocery</v>
+        <v>Al Masa Grocery</v>
       </c>
       <c r="G55" t="str">
         <v>TAN-330-24</v>
@@ -6764,7 +6764,7 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Al Safa Foodstuff</v>
+        <v>Al Masa Foodstuff</v>
       </c>
       <c r="G182" t="str">
         <v>TAN-19L</v>
@@ -6799,7 +6799,7 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Al Safa Foodstuff</v>
+        <v>Al Masa Foodstuff</v>
       </c>
       <c r="G183" t="str">
         <v>TIS-FAC-30</v>

--- a/apps/web/tests/fixtures/nmwc/orders-150.xlsx
+++ b/apps/web/tests/fixtures/nmwc/orders-150.xlsx
@@ -7569,7 +7569,7 @@
         <v>B01</v>
       </c>
       <c r="F205" t="str">
-        <v>Al Noor Grocery - Ruwi</v>
+        <v>Al Nimr Grocery - Ruwi</v>
       </c>
       <c r="G205" t="str">
         <v>TAN-5L-4</v>
@@ -7604,7 +7604,7 @@
         <v>B01</v>
       </c>
       <c r="F206" t="str">
-        <v>Al Noor Grocery - Ruwi</v>
+        <v>Al Nimr Grocery - Ruwi</v>
       </c>
       <c r="G206" t="str">
         <v>TAN-500-24</v>
@@ -11909,7 +11909,7 @@
         <v>B02</v>
       </c>
       <c r="F329" t="str">
-        <v>Al Noor Grocery - Al Ansab</v>
+        <v>Al Nimr Grocery - Al Ansab</v>
       </c>
       <c r="G329" t="str">
         <v>TAN-1500-6</v>
@@ -11944,7 +11944,7 @@
         <v>B02</v>
       </c>
       <c r="F330" t="str">
-        <v>Al Noor Grocery - Al Ansab</v>
+        <v>Al Nimr Grocery - Al Ansab</v>
       </c>
       <c r="G330" t="str">
         <v>JAB-500-24</v>

--- a/apps/web/tests/fixtures/nmwc/orders-150.xlsx
+++ b/apps/web/tests/fixtures/nmwc/orders-150.xlsx
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Al Safa Grocery</v>
+        <v>Al Masa Grocery</v>
       </c>
       <c r="G53" t="str">
         <v>TAN-500-24</v>
@@ -2284,7 +2284,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Al Safa Grocery</v>
+        <v>Al Masa Grocery</v>
       </c>
       <c r="G54" t="str">
         <v>TAN-1500-6</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Al Safa Grocery</v>
+        <v>Al Masa Grocery</v>
       </c>
       <c r="G55" t="str">
         <v>TAN-330-24</v>
@@ -6764,7 +6764,7 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Al Safa Foodstuff</v>
+        <v>Al Masa Foodstuff</v>
       </c>
       <c r="G182" t="str">
         <v>TAN-19L</v>
@@ -6799,7 +6799,7 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Al Safa Foodstuff</v>
+        <v>Al Masa Foodstuff</v>
       </c>
       <c r="G183" t="str">
         <v>TIS-FAC-30</v>
@@ -7569,7 +7569,7 @@
         <v>B01</v>
       </c>
       <c r="F205" t="str">
-        <v>Al Noor Grocery - Ruwi</v>
+        <v>Al Nimr Grocery - Ruwi</v>
       </c>
       <c r="G205" t="str">
         <v>TAN-5L-4</v>
@@ -7604,7 +7604,7 @@
         <v>B01</v>
       </c>
       <c r="F206" t="str">
-        <v>Al Noor Grocery - Ruwi</v>
+        <v>Al Nimr Grocery - Ruwi</v>
       </c>
       <c r="G206" t="str">
         <v>TAN-500-24</v>
@@ -11909,7 +11909,7 @@
         <v>B02</v>
       </c>
       <c r="F329" t="str">
-        <v>Al Noor Grocery - Al Ansab</v>
+        <v>Al Nimr Grocery - Al Ansab</v>
       </c>
       <c r="G329" t="str">
         <v>TAN-1500-6</v>
@@ -11944,7 +11944,7 @@
         <v>B02</v>
       </c>
       <c r="F330" t="str">
-        <v>Al Noor Grocery - Al Ansab</v>
+        <v>Al Nimr Grocery - Al Ansab</v>
       </c>
       <c r="G330" t="str">
         <v>JAB-500-24</v>
